--- a/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣重要交通觀光景點下車人數統計.xlsx
+++ b/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣重要交通觀光景點下車人數統計.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">年份</t>
   </si>
@@ -20,7 +20,10 @@
     <t xml:space="preserve">三仙台遊憩區</t>
   </si>
   <si>
-    <t xml:space="preserve">卑南初鹿地區</t>
+    <t xml:space="preserve">初鹿地區</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加路蘭遊憩區</t>
   </si>
   <si>
     <t xml:space="preserve">富岡漁港及小野柳</t>
@@ -401,6 +404,9 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -413,24 +419,27 @@
         <v>11476</v>
       </c>
       <c r="D2" t="n">
+        <v>3105</v>
+      </c>
+      <c r="E2" t="n">
         <v>20987</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>3389</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1516</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>88008</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>180075</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>19433</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>505</v>
       </c>
     </row>
@@ -445,24 +454,27 @@
         <v>11655</v>
       </c>
       <c r="D3" t="n">
+        <v>5075</v>
+      </c>
+      <c r="E3" t="n">
         <v>34935</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>3569</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2047</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>112591</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>211405</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>21717</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>491</v>
       </c>
     </row>
@@ -477,24 +489,27 @@
         <v>11320</v>
       </c>
       <c r="D4" t="n">
+        <v>3597</v>
+      </c>
+      <c r="E4" t="n">
         <v>26625</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3417</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1240</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>99514</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>185823</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>17594</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>701</v>
       </c>
     </row>

--- a/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣重要交通觀光景點下車人數統計.xlsx
+++ b/交通觀光景點分析 + 鄉鎮際搭乘分析/datasets/112-114/臺東縣重要交通觀光景點下車人數統計.xlsx
@@ -1,64 +1,133 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\交通觀光景點分析 + 鄉鎮際搭乘分析\datasets\112-114\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEB87B3-6DD7-4F83-A099-EBE0E517D9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="12480" yWindow="690" windowWidth="14505" windowHeight="14490" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="觀光景點人數統計" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="觀光景點人數統計" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t xml:space="preserve">年份</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三仙台遊憩區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">初鹿地區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加路蘭遊憩區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">富岡漁港及小野柳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">池上車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">臺東航空站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">臺東車站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">臺東轉運站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">都蘭遊憩區</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鹿野高台</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+  <si>
+    <t>年份</t>
+  </si>
+  <si>
+    <t>三仙台遊憩區</t>
+  </si>
+  <si>
+    <t>初鹿地區</t>
+  </si>
+  <si>
+    <t>加路蘭遊憩區</t>
+  </si>
+  <si>
+    <t>富岡漁港及小野柳</t>
+  </si>
+  <si>
+    <t>池上車站</t>
+  </si>
+  <si>
+    <t>臺東航空站</t>
+  </si>
+  <si>
+    <t>臺東車站</t>
+  </si>
+  <si>
+    <t>臺東轉運站</t>
+  </si>
+  <si>
+    <t>都蘭遊憩區</t>
+  </si>
+  <si>
+    <t>鹿野高台</t>
+  </si>
+  <si>
+    <t>富岡漁港及小野柳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加路蘭遊憩區</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>113</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>114</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,13 +150,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -369,11 +450,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -408,113 +492,565 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:11">
+      <c r="A2">
         <v>112</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>2773</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>11476</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>3105</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>20987</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>3389</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>1516</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>88008</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>180075</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>19433</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>505</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:11">
+      <c r="A3">
         <v>113</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>9535</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>11655</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>5075</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>34935</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>3569</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>2047</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>112591</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>211405</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>21717</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>491</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:11">
+      <c r="A4">
         <v>114</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>6203</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>11320</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>3597</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>26625</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>3417</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>1240</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>99514</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>185823</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>17594</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>701</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>112</v>
+      </c>
+      <c r="C8">
+        <v>113</v>
+      </c>
+      <c r="D8">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>2773</v>
+      </c>
+      <c r="C9">
+        <v>9535</v>
+      </c>
+      <c r="D9">
+        <v>6203</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.4390000000000001</v>
+      </c>
+      <c r="F9" s="1">
+        <v>-0.34899999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>11476</v>
+      </c>
+      <c r="C10">
+        <v>11655</v>
+      </c>
+      <c r="D10">
+        <v>11320</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>3105</v>
+      </c>
+      <c r="C11">
+        <v>5075</v>
+      </c>
+      <c r="D11">
+        <v>3597</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-0.29099999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>20987</v>
+      </c>
+      <c r="C12">
+        <v>34935</v>
+      </c>
+      <c r="D12">
+        <v>26625</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="F12" s="1">
+        <v>-0.23799999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>3389</v>
+      </c>
+      <c r="C13">
+        <v>3569</v>
+      </c>
+      <c r="D13">
+        <v>3417</v>
+      </c>
+      <c r="E13" s="1">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F13" s="1">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>1516</v>
+      </c>
+      <c r="C14">
+        <v>2047</v>
+      </c>
+      <c r="D14">
+        <v>1240</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="F14" s="1">
+        <v>-0.39400000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>88008</v>
+      </c>
+      <c r="C15">
+        <v>112591</v>
+      </c>
+      <c r="D15">
+        <v>99514</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="F15" s="1">
+        <v>-0.11600000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>180075</v>
+      </c>
+      <c r="C16">
+        <v>211405</v>
+      </c>
+      <c r="D16">
+        <v>185823</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="F16" s="1">
+        <v>-0.121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <v>19433</v>
+      </c>
+      <c r="C17">
+        <v>21717</v>
+      </c>
+      <c r="D17">
+        <v>17594</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="F17" s="1">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>505</v>
+      </c>
+      <c r="C18">
+        <v>491</v>
+      </c>
+      <c r="D18">
+        <v>701</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.42799999999999999</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C49309-DE73-457D-950F-C932F720D515}">
+  <dimension ref="A2:F12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>112</v>
+      </c>
+      <c r="C2">
+        <v>113</v>
+      </c>
+      <c r="D2">
+        <v>114</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2">
+        <v>180075</v>
+      </c>
+      <c r="C3" s="2">
+        <v>211405</v>
+      </c>
+      <c r="D3" s="2">
+        <v>185823</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="F3" s="1">
+        <v>-0.121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>88008</v>
+      </c>
+      <c r="C4" s="2">
+        <v>112591</v>
+      </c>
+      <c r="D4" s="2">
+        <v>99514</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="F4" s="1">
+        <v>-0.11600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>20987</v>
+      </c>
+      <c r="C5" s="2">
+        <v>34935</v>
+      </c>
+      <c r="D5" s="2">
+        <v>26625</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="F5" s="1">
+        <v>-0.23799999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2">
+        <v>19433</v>
+      </c>
+      <c r="C6" s="2">
+        <v>21717</v>
+      </c>
+      <c r="D6" s="2">
+        <v>17594</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="F6" s="1">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2">
+        <v>11476</v>
+      </c>
+      <c r="C7" s="2">
+        <v>11655</v>
+      </c>
+      <c r="D7" s="2">
+        <v>11320</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>-2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2773</v>
+      </c>
+      <c r="C8" s="2">
+        <v>9535</v>
+      </c>
+      <c r="D8" s="2">
+        <v>6203</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2.4390000000000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>-0.34899999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3105</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5075</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3597</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="F9" s="1">
+        <v>-0.29099999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3389</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3569</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3417</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1516</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2047</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1240</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="F11" s="1">
+        <v>-0.39400000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>505</v>
+      </c>
+      <c r="C12" s="2">
+        <v>491</v>
+      </c>
+      <c r="D12" s="2">
+        <v>701</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.42799999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F13">
+    <sortCondition descending="1" ref="D4:D13"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>